--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/30 20:27:02</t>
+          <t>09/22 16:25:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>121000</t>
+          <t>203000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14404.76</t>
+          <t>23882.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/29 14:07:29</t>
+          <t>08/30 20:27:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>121000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8504.94</t>
+          <t>14404.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/26 20:06:13</t>
+          <t>08/29 14:07:29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>96000</t>
+          <t>73993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11497.01</t>
+          <t>8504.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/25 13:27:02</t>
+          <t>08/26 20:06:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>96000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7125.75</t>
+          <t>11497.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,166 +243,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08/25 13:27:02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>61994</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7125.75</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>08/25 12:00:08</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>72595</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>8344.25</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -424,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -451,83 +466,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>425582</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>49876.71</t>
+          <t>628582</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>49875</t>
+          <t>73759.06</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>49875</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1.71</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>23884.06</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -412,12 +412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>09/22 17:45:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -439,12 +439,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,83 +493,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>628582</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>73759.06</t>
+          <t>628582</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>49875</t>
+          <t>73759.06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>73757</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>23884.06</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2.06</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22 16:25:12</t>
+          <t>10/18 18:48:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>203000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23882.35</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/30 20:27:02</t>
+          <t>09/22 16:25:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>121000</t>
+          <t>203000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14404.76</t>
+          <t>23882.35</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/29 14:07:29</t>
+          <t>08/30 20:27:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>121000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8504.94</t>
+          <t>14404.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/26 20:06:13</t>
+          <t>08/29 14:07:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>96000</t>
+          <t>73993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11497.01</t>
+          <t>8504.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/25 13:27:02</t>
+          <t>08/26 20:06:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>96000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7125.75</t>
+          <t>11497.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,166 +285,181 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08/25 13:27:02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>61994</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7125.75</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>08/25 12:00:08</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>72595</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>8344.25</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/22 17:45:18</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>09/22 17:45:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -466,12 +481,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -493,12 +508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -520,83 +535,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>628582</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>73759.06</t>
+          <t>728582</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>85523.77</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>73757</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2.06</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>11766.77</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/18 18:48:44</t>
+          <t>10/18 19:02:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/22 16:25:12</t>
+          <t>10/18 18:48:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>203000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23882.35</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/30 20:27:02</t>
+          <t>09/22 16:25:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>121000</t>
+          <t>203000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14404.76</t>
+          <t>23882.35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/29 14:07:29</t>
+          <t>08/30 20:27:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>121000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8504.94</t>
+          <t>14404.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/26 20:06:13</t>
+          <t>08/29 14:07:29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>96000</t>
+          <t>73993</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11497.01</t>
+          <t>8504.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/25 13:27:02</t>
+          <t>08/26 20:06:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>96000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7125.75</t>
+          <t>11497.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>08/25 13:27:02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>61994</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7125.75</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>08/25 12:00:08</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>72595</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>8344.25</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/22 17:45:18</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>09/22 17:45:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -508,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -535,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -562,83 +577,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>728582</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>85523.77</t>
+          <t>828582</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>97571.96</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>73757</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>11766.77</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>23814.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -496,12 +496,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/22 17:45:18</t>
+          <t>10/18 20:38:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -523,12 +523,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>09/22 17:45:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,83 +604,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>828582</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>97571.96</t>
+          <t>828582</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>97571.96</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>85805</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>23814.96</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>11766.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/18 19:02:57</t>
+          <t>10/20 18:57:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>652.86</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/18 18:48:44</t>
+          <t>10/18 19:02:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/22 16:25:12</t>
+          <t>10/18 18:48:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>203000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23882.35</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/30 20:27:02</t>
+          <t>09/22 16:25:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>121000</t>
+          <t>203000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14404.76</t>
+          <t>23882.35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/29 14:07:29</t>
+          <t>08/30 20:27:02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>121000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8504.94</t>
+          <t>14404.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/26 20:06:13</t>
+          <t>08/29 14:07:29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>96000</t>
+          <t>73993</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11497.01</t>
+          <t>8504.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/25 13:27:02</t>
+          <t>08/26 20:06:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>96000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7125.75</t>
+          <t>11497.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>08/25 13:27:02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>61994</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>7125.75</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>08/25 12:00:08</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>72595</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>8344.25</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/18 20:38:02</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/22 17:45:18</t>
+          <t>10/18 20:38:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>09/22 17:45:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,83 +646,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>828582</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>97571.96</t>
+          <t>833609</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>85805</t>
+          <t>98224.82</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>85805</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>11766.96</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12419.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -538,12 +538,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/18 20:38:02</t>
+          <t>10/21 16:30:06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>-652</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -565,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22 17:45:18</t>
+          <t>10/18 20:38:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -592,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>09/22 17:45:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,83 +673,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>833609</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>98224.82</t>
+          <t>833609</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>85805</t>
+          <t>98224.82</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>85153</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>12419.82</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>13071.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/20 18:57:54</t>
+          <t>10/21 16:30:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>169245</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>652.86</t>
+          <t>21979.87</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/18 19:02:57</t>
+          <t>10/20 18:57:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>652.86</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/18 18:48:44</t>
+          <t>10/18 19:02:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/22 16:25:12</t>
+          <t>10/18 18:48:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>203000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23882.35</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/30 20:27:02</t>
+          <t>09/22 16:25:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>121000</t>
+          <t>203000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14404.76</t>
+          <t>23882.35</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/29 14:07:29</t>
+          <t>08/30 20:27:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>121000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8504.94</t>
+          <t>14404.76</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/26 20:06:13</t>
+          <t>08/29 14:07:29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>96000</t>
+          <t>73993</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11497.01</t>
+          <t>8504.94</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/25 13:27:02</t>
+          <t>08/26 20:06:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>96000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7125.75</t>
+          <t>11497.01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>08/25 13:27:02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>61994</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7125.75</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>08/25 12:00:08</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>72595</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>8344.25</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10/21 16:30:06</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-652</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/18 20:38:02</t>
+          <t>10/21 16:30:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>-652</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -580,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22 17:45:18</t>
+          <t>10/18 20:38:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>09/22 17:45:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,83 +715,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>833609</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>98224.82</t>
+          <t>1002854</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>85153</t>
+          <t>120204.69</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>85153</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>13071.82</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>35051.69</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/21 16:30:06</t>
+          <t>10/21 16:47:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-652</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/18 20:38:02</t>
+          <t>10/21 16:30:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>-652</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/22 17:45:18</t>
+          <t>10/18 20:38:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>09/22 17:45:18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,83 +742,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1002854</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>120204.69</t>
+          <t>1002854</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>85153</t>
+          <t>120204.69</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>107784</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>35051.69</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>12420.69</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/21 16:30:56</t>
+          <t>10/22 16:43:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>169245</t>
+          <t>152715</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21979.87</t>
+          <t>19833.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/20 18:57:54</t>
+          <t>10/21 16:30:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>169245</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>652.86</t>
+          <t>21979.87</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/18 19:02:57</t>
+          <t>10/20 18:57:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>652.86</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/18 18:48:44</t>
+          <t>10/18 19:02:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/22 16:25:12</t>
+          <t>10/18 18:48:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>203000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23882.35</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/30 20:27:02</t>
+          <t>09/22 16:25:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>121000</t>
+          <t>203000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14404.76</t>
+          <t>23882.35</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/29 14:07:29</t>
+          <t>08/30 20:27:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>121000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8504.94</t>
+          <t>14404.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/26 20:06:13</t>
+          <t>08/29 14:07:29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>96000</t>
+          <t>73993</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11497.01</t>
+          <t>8504.94</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/25 13:27:02</t>
+          <t>08/26 20:06:13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>96000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7125.75</t>
+          <t>11497.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>08/25 13:27:02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>61994</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7125.75</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>08/25 12:00:08</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>72595</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>8344.25</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10/21 16:47:31</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22631</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/21 16:30:06</t>
+          <t>10/21 16:47:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-652</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +637,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10/18 20:38:02</t>
+          <t>10/21 16:30:06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>-652</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +664,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/22 17:45:18</t>
+          <t>10/18 20:38:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>09/22 17:45:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,83 +784,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1002854</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>120204.69</t>
+          <t>1155569</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>107784</t>
+          <t>140037.81</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>107784</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>12420.69</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>32253.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
+++ b/bills/JXZFSP01/-5488102317/7aad43770c4663c342d39def8dde10528d2adea40c118d4f33c29b5a59b5fb95/bill-all.xlsx
@@ -622,12 +622,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/21 16:47:31</t>
+          <t>10/22 19:23:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22631</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -649,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10/21 16:30:06</t>
+          <t>10/21 16:47:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-652</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10/18 20:38:02</t>
+          <t>10/21 16:30:06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>-652</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/22 17:45:18</t>
+          <t>10/18 20:38:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/30 23:02:44</t>
+          <t>09/22 17:45:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -757,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/29 14:29:56</t>
+          <t>08/30 23:02:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -784,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/26 21:53:10</t>
+          <t>08/29 14:29:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,83 +811,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>08/26 21:53:10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>08/25 14:00:04</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>15470</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1155569</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>140037.81</t>
+          <t>1155569</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>107784</t>
+          <t>140037.81</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>127617</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>32253.81</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>12420.81</t>
         </is>
       </c>
     </row>
